--- a/data/credit_bond_2026-10-13.xlsx
+++ b/data/credit_bond_2026-10-13.xlsx
@@ -700,7 +700,11 @@
           <t>10-13 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102683969.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2+2</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.4900/2.4300</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -779,7 +783,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>2.35%~2.45%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -920,7 +928,11 @@
           <t>10-13 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102683970.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -999,7 +1011,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.58%~2.68%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>

--- a/data/credit_bond_2026-10-13.xlsx
+++ b/data/credit_bond_2026-10-13.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-13" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-13</t>
+          <t>数据来源：DM    2026-10-14</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.4758</t>
+          <t>2.4710</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2.4900/2.4300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C 29.50</t>
+          <t>C 29.91</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -777,7 +777,9 @@
         </is>
       </c>
       <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="V3" s="4" t="n">
+        <v>2.69</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -981,7 +983,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 29.50</t>
+          <t>C 29.91</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-13.xlsx
+++ b/data/credit_bond_2026-10-13.xlsx
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>5.3</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.05 ~ 2.75</t>
@@ -943,7 +945,9 @@
       <c r="E4" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.25 ~ 2.95</t>

--- a/data/credit_bond_2026-10-13.xlsx
+++ b/data/credit_bond_2026-10-13.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-14" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-15" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-14</t>
+          <t>数据来源：DM    2026-10-15</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN006A</t>
+          <t>26金融街MTN006</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -714,15 +714,19 @@
         <v>5.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>5.3</v>
+        <v>10.3</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.05 ~ 2.75</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>123.99</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2.50</t>
@@ -755,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C 29.91</t>
+          <t>C 28.88</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -778,7 +782,9 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V3" s="4" t="n">
         <v>2.69</v>
       </c>
@@ -835,7 +841,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第六期中期票据(品种一)</t>
+          <t>金融街控股股份有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -924,7 +930,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN006B</t>
+          <t>26金融街MTN006B(取消发行)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -934,7 +940,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683970.IB</t>
+          <t>DY102683970.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -945,9 +951,7 @@
       <c r="E4" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>2.25 ~ 2.95</t>
@@ -987,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 29.91</t>
+          <t>C 28.88</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1065,7 +1069,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第六期中期票据(品种二)</t>
+          <t>金融街控股股份有限公司2026年度第六期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1126,7 +1130,7 @@
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t>2029-10-14</t>
+          <t/>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-13.xlsx
+++ b/data/credit_bond_2026-10-13.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-15" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-16" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-15</t>
+          <t>数据来源：DM    2026-10-16</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN006</t>
+          <t>26金融街MTN006B(取消发行)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,49 +702,43 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102683969.IB</t>
+          <t>DY102683970.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>10.3</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2.05 ~ 2.75</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>123.99</v>
-      </c>
+          <t>2.25 ~ 2.95</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>23金街11</t>
+          <t>26金融街MTN004B</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>1.93Y</t>
+          <t>2.83Y+2.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.4710</t>
+          <t>2.7184</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -759,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C 28.88</t>
+          <t>C+ 30.46</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -782,12 +776,8 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="U3" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>2.69</v>
-      </c>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -795,7 +785,7 @@
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2.35%~2.45%</t>
+          <t>2.58%~2.68%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -841,7 +831,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第六期中期票据</t>
+          <t>金融街控股股份有限公司2026年度第六期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -851,7 +841,7 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2030-10-14</t>
+          <t>2031-10-14</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
@@ -902,7 +892,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2028-10-14</t>
+          <t/>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -930,7 +920,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN006B(取消发行)</t>
+          <t>26金融街MTN006</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -940,43 +930,49 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DY102683970.IB</t>
+          <t>102683969.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>5.3</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>10.3</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2.25 ~ 2.95</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+          <t>2.05 ~ 2.75</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>123.99</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26金融街MTN004B</t>
+          <t>23金街11</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.83Y+2.00Y</t>
+          <t>1.93Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.7184</t>
+          <t>2.4710</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 28.88</t>
+          <t>C+ 30.46</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1014,8 +1010,12 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.6019</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>2.69</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.58%~2.68%</t>
+          <t>2.35%~2.45%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>金融街控股股份有限公司2026年度第六期中期票据(品种二)(取消发行)</t>
+          <t>金融街控股股份有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-10-14</t>
+          <t>2030-10-14</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-10-14</t>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-13.xlsx
+++ b/data/credit_bond_2026-10-13.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-16" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-19" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-16</t>
+          <t>数据来源：DM    2026-10-19</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.46</t>
+          <t>C 28.07</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.46</t>
+          <t>C 28.07</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
